--- a/data/trans_orig/Q5410-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2007</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>32677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66681</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73730</t>
+          <t>73716</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>61577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89744</t>
+          <t>90007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155514</t>
+          <t>155299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164529</t>
+          <t>163525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49135</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55122</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>62585</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72310</t>
+          <t>72318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117572</t>
+          <t>117774</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127415</t>
+          <t>127475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>32175</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>40136</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56591</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67069</t>
+          <t>67126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45391</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115580</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>831</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100817</t>
+          <t>101581</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108362</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>116221</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>213599</t>
+          <t>213049</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>222010</t>
+          <t>222025</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15336</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>110059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>111893</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>135307</t>
+          <t>135303</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149472</t>
+          <t>149214</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>246429</t>
+          <t>246982</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>261223</t>
+          <t>261051</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>486727</t>
+          <t>488130</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>498058</t>
+          <t>498253</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>641032</t>
+          <t>640852</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>661291</t>
+          <t>661170</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1134200</t>
+          <t>1133421</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1156736</t>
+          <t>1157292</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2012</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>39243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>39483</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47785</t>
+          <t>47869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82812</t>
+          <t>81709</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91213</t>
+          <t>91174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>17196</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67389</t>
+          <t>67120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78144</t>
+          <t>78148</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84584</t>
+          <t>84647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97817</t>
+          <t>98673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156294</t>
+          <t>158142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174648</t>
+          <t>174664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>16084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48592</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54801</t>
+          <t>54771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65923</t>
+          <t>65880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76683</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117535</t>
+          <t>117340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130416</t>
+          <t>130246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58285</t>
+          <t>59133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79310</t>
+          <t>79782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>140323</t>
+          <t>141239</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43484</t>
+          <t>43695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68818</t>
+          <t>68472</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78604</t>
+          <t>79233</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9755</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44280</t>
+          <t>44600</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60380</t>
+          <t>59642</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69124</t>
+          <t>69121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>109008</t>
+          <t>109149</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>119764</t>
+          <t>119771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17460</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96786</t>
+          <t>97027</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110241</t>
+          <t>110186</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>129816</t>
+          <t>129341</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139100</t>
+          <t>139805</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>231608</t>
+          <t>232122</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>248037</t>
+          <t>247224</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9578</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>113934</t>
+          <t>113180</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>150368</t>
+          <t>149904</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>162012</t>
+          <t>161261</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>268651</t>
+          <t>268499</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>281681</t>
+          <t>280823</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12012</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39953</t>
+          <t>39621</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>52335</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>522180</t>
+          <t>524191</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>543702</t>
+          <t>544707</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>684793</t>
+          <t>686967</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>712782</t>
+          <t>713631</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1219192</t>
+          <t>1217257</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1252618</t>
+          <t>1251653</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2016</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>32282</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>42062</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78085</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86590</t>
+          <t>86662</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82151</t>
+          <t>82861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108430</t>
+          <t>108484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193119</t>
+          <t>193904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>56098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128455</t>
+          <t>129983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141423</t>
+          <t>142146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59283</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84140</t>
+          <t>84607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146953</t>
+          <t>146329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155329</t>
+          <t>155268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40404</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48476</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90724</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92612</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11051</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>35692</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45106</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55947</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65187</t>
+          <t>65102</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95750</t>
+          <t>95090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108660</t>
+          <t>108347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>871</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103087</t>
+          <t>103792</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111290</t>
+          <t>111293</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136140</t>
+          <t>135955</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>146362</t>
+          <t>146325</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>242410</t>
+          <t>242804</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>255489</t>
+          <t>255865</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>130027</t>
+          <t>130063</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>168445</t>
+          <t>168254</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>300848</t>
+          <t>301200</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>309653</t>
+          <t>309664</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>38215</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>564430</t>
+          <t>565250</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>580273</t>
+          <t>580081</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>740948</t>
+          <t>742830</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>763074</t>
+          <t>763494</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1313182</t>
+          <t>1313810</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1339618</t>
+          <t>1340273</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la caca (incontinencia) en 2023</t>
+          <t>Población según si se le escapa la caca (incontinencia) en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62495</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76422</t>
+          <t>75794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117472</t>
+          <t>115891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126000</t>
+          <t>125621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196707</t>
+          <t>196988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205634</t>
+          <t>206082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>528</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68574</t>
+          <t>68111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72930</t>
+          <t>72921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81534</t>
+          <t>81892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86492</t>
+          <t>86504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152921</t>
+          <t>152708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>444</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70887</t>
+          <t>70762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98157</t>
+          <t>98597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102753</t>
+          <t>102755</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>171406</t>
+          <t>171332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>177013</t>
+          <t>176751</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>30095</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34334</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48939</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>54641</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81474</t>
+          <t>81461</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88385</t>
+          <t>88343</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54348</t>
+          <t>54392</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59006</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58384</t>
+          <t>58664</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63228</t>
+          <t>63413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114906</t>
+          <t>114873</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121265</t>
+          <t>121296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>525</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117056</t>
+          <t>117109</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122505</t>
+          <t>122513</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>318737</t>
+          <t>318957</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>337694</t>
+          <t>337607</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>443073</t>
+          <t>443062</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>460177</t>
+          <t>460412</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>539</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>540</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>19164</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>139088</t>
+          <t>138547</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>145244</t>
+          <t>145222</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>165861</t>
+          <t>165397</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>176700</t>
+          <t>176975</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>307011</t>
+          <t>307452</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>319962</t>
+          <t>320444</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17421,7 +17421,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>22363</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>42867</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>54644</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>628893</t>
+          <t>627740</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>640245</t>
+          <t>639778</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>974870</t>
+          <t>975036</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1008764</t>
+          <t>1011681</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1608970</t>
+          <t>1611057</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1644045</t>
+          <t>1645514</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5410-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5410-Provincia-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29790</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>33186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>65867</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>73737</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61577</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>90624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155299</t>
+          <t>156288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163525</t>
+          <t>163528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>73172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117774</t>
+          <t>117934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127475</t>
+          <t>127436</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>31962</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>40127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57162</t>
+          <t>56646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67126</t>
+          <t>66915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>101581</t>
+          <t>100968</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108100</t>
+          <t>108857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116221</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>213049</t>
+          <t>213867</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>222025</t>
+          <t>222000</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>135303</t>
+          <t>135435</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149214</t>
+          <t>149248</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>246982</t>
+          <t>247634</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>261051</t>
+          <t>261314</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>488130</t>
+          <t>487510</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>498253</t>
+          <t>498172</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>640852</t>
+          <t>639905</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>661170</t>
+          <t>661311</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1133421</t>
+          <t>1133097</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1157292</t>
+          <t>1156210</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39243</t>
+          <t>38430</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39483</t>
+          <t>39552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47869</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81709</t>
+          <t>82506</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91174</t>
+          <t>91260</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67120</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78148</t>
+          <t>78142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84647</t>
+          <t>83659</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98673</t>
+          <t>97682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158142</t>
+          <t>158391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174664</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>47549</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54771</t>
+          <t>54787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65880</t>
+          <t>64852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76703</t>
+          <t>76644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117340</t>
+          <t>117256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130246</t>
+          <t>130463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59133</t>
+          <t>58565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>78560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>141239</t>
+          <t>142539</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30454</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43695</t>
+          <t>43776</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68472</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79233</t>
+          <t>78491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44600</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59642</t>
+          <t>60485</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69121</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>109149</t>
+          <t>109004</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>119771</t>
+          <t>119795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97027</t>
+          <t>97758</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110186</t>
+          <t>110246</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>129341</t>
+          <t>130024</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139805</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>232122</t>
+          <t>232057</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>247224</t>
+          <t>247151</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>113180</t>
+          <t>112866</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>149904</t>
+          <t>150999</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>161261</t>
+          <t>162110</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>268499</t>
+          <t>268437</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>280823</t>
+          <t>280970</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>31211</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39621</t>
+          <t>41375</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31013</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>52133</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>524191</t>
+          <t>522665</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>544707</t>
+          <t>543920</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>686967</t>
+          <t>689004</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>713631</t>
+          <t>714049</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1217257</t>
+          <t>1219230</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1251653</t>
+          <t>1252825</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>32399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>42744</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78705</t>
+          <t>77626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86662</t>
+          <t>86658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82861</t>
+          <t>82179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108484</t>
+          <t>108439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193904</t>
+          <t>194997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56098</t>
+          <t>57377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129983</t>
+          <t>129939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142146</t>
+          <t>141450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58693</t>
+          <t>58439</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84607</t>
+          <t>84983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146329</t>
+          <t>146704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155268</t>
+          <t>155314</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>36713</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>55411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65102</t>
+          <t>65307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95090</t>
+          <t>95434</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108347</t>
+          <t>108674</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>932</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>103792</t>
+          <t>103856</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111293</t>
+          <t>111263</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>135955</t>
+          <t>135473</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>146325</t>
+          <t>146339</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>242804</t>
+          <t>242409</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>255865</t>
+          <t>255467</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>130063</t>
+          <t>129537</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>168254</t>
+          <t>167610</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>301200</t>
+          <t>301287</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>309664</t>
+          <t>309667</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11628</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38215</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>565250</t>
+          <t>563887</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>580081</t>
+          <t>580085</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>742830</t>
+          <t>741490</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>763494</t>
+          <t>763083</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1313810</t>
+          <t>1314356</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1340273</t>
+          <t>1340697</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -14284,12 +14284,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,17 +14352,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -14430,27 +14430,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79844</t>
+          <t>87447</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75794</t>
+          <t>84646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>122609</t>
+          <t>128527</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115891</t>
+          <t>122036</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125621</t>
+          <t>131995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>202451</t>
+          <t>215974</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196988</t>
+          <t>209499</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206082</t>
+          <t>219611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,17 +14730,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -14783,12 +14783,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14843,17 +14843,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -14886,32 +14886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>71655</t>
+          <t>70533</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68111</t>
+          <t>67596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72921</t>
+          <t>71760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>84873</t>
+          <t>83277</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81892</t>
+          <t>80052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86504</t>
+          <t>84906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,17 +14956,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>156528</t>
+          <t>153810</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152708</t>
+          <t>150170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159186</t>
+          <t>156084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>837</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -15161,12 +15161,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>837</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -15196,12 +15196,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>844</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>464</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -15342,27 +15342,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73914</t>
+          <t>82312</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70762</t>
+          <t>78960</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>101082</t>
+          <t>107886</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98597</t>
+          <t>104997</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102755</t>
+          <t>109400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>174995</t>
+          <t>190197</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>171332</t>
+          <t>186676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176751</t>
+          <t>192319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>487</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -15798,32 +15798,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>32018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52398</t>
+          <t>54482</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>51165</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54641</t>
+          <t>57144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15868,32 +15868,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>85311</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81461</t>
+          <t>84738</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88343</t>
+          <t>92266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>760</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,32 +16098,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -16151,12 +16151,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>687</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -16186,12 +16186,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16211,32 +16211,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>57122</t>
+          <t>57128</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54392</t>
+          <t>54209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>58905</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>61421</t>
+          <t>63263</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58664</t>
+          <t>60234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63413</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,32 +16324,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>118542</t>
+          <t>120389</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114873</t>
+          <t>116835</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121296</t>
+          <t>123132</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16519,32 +16519,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -16597,32 +16597,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16632,32 +16632,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -16710,32 +16710,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>120954</t>
+          <t>148609</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117109</t>
+          <t>144070</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122513</t>
+          <t>150447</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>332469</t>
+          <t>157025</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>318957</t>
+          <t>151424</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>337607</t>
+          <t>160817</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>453423</t>
+          <t>305634</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>443062</t>
+          <t>299524</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>460412</t>
+          <t>310207</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>338685</t>
+          <t>164166</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>338685</t>
+          <t>164166</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>338685</t>
+          <t>164166</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>461939</t>
+          <t>315507</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>461939</t>
+          <t>315507</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>461939</t>
+          <t>315507</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16975,32 +16975,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17010,22 +17010,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -17053,32 +17053,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17088,32 +17088,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -17166,32 +17166,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>142789</t>
+          <t>158856</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>138547</t>
+          <t>154796</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>145222</t>
+          <t>161510</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17201,32 +17201,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>171936</t>
+          <t>195109</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>165397</t>
+          <t>186323</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>176975</t>
+          <t>201075</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>314725</t>
+          <t>353965</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>307452</t>
+          <t>344988</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>320444</t>
+          <t>360481</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>146475</t>
+          <t>162902</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>333117</t>
+          <t>375668</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333117</t>
+          <t>375668</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>333117</t>
+          <t>375668</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,32 +17396,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>31438</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>44205</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>47485</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>28321</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>59237</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>635090</t>
+          <t>700361</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>627740</t>
+          <t>693034</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>639778</t>
+          <t>705665</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>990196</t>
+          <t>854843</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>975036</t>
+          <t>843069</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1011681</t>
+          <t>864204</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1625287</t>
+          <t>1555204</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1611057</t>
+          <t>1542681</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1645514</t>
+          <t>1565827</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1033292</t>
+          <t>902740</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1682866</t>
+          <t>1618478</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
